--- a/Coordenates.xlsx
+++ b/Coordenates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\OneDrive\Escritorio\Personal\Catatumbo\Project_Catatumbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E57E8B4-A303-40E6-AC96-9D69D1D286C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AABD70E-E7C2-443C-BD43-51F082740600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{83489CD3-D6C7-4678-AA3D-DB19114C5D5E}"/>
   </bookViews>
@@ -875,9 +875,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.00000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.0000000"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0000000"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -941,15 +941,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -963,7 +963,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -16182,7 +16182,6 @@
       <c r="BL761" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BQ15" xr:uid="{7A44DDAD-AE50-4664-AB6E-6641F4600798}"/>
   <hyperlinks>
     <hyperlink ref="AU2" r:id="rId1" xr:uid="{33C0D228-AC87-4B8B-905C-75B9D57A2258}"/>
     <hyperlink ref="AU15" r:id="rId2" xr:uid="{666CDE17-677E-4A1E-8F05-A1EB52181280}"/>
